--- a/blackjack_stappen.xlsx
+++ b/blackjack_stappen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fspr805\Documents\Git projecten\OOSD I\H05\H05_oefOpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A9C0052-383A-43B0-889D-AEF91C92C864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D74CBED-595C-4577-B25B-C97D815B68CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="71">
   <si>
     <t>wat?</t>
   </si>
@@ -317,7 +317,22 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -1158,6 +1173,16 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
@@ -1541,6 +1566,16 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
       <c r="G16" t="s">
         <v>16</v>
       </c>
@@ -1570,6 +1605,16 @@
       </c>
     </row>
     <row r="17" spans="4:15" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
       <c r="G17" t="s">
         <v>16</v>
       </c>
@@ -1677,6 +1722,16 @@
       </c>
     </row>
     <row r="20" spans="4:15" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
@@ -1709,6 +1764,16 @@
       </c>
     </row>
     <row r="21" spans="4:15" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
@@ -2151,14 +2216,9 @@
   </sheetData>
   <autoFilter ref="D1:O67" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="D2:F6 D8:F37">
-    <cfRule type="expression" dxfId="1" priority="9">
+  <conditionalFormatting sqref="D2:F31">
+    <cfRule type="expression" dxfId="2" priority="9">
       <formula>$F2=$F1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:F7">
-    <cfRule type="expression" dxfId="0" priority="11">
-      <formula>$F7=$F5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
